--- a/docs/crookedile-card-art-prompts.xlsx
+++ b/docs/crookedile-card-art-prompts.xlsx
@@ -3247,7 +3247,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Hand Me Down</t>
+          <t>Last Season</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>one oversized hand-me-down jacket flung forward with motion arcs, one emerald green accent</t>
+          <t>one last-season designer handbag flung forward with motion arcs, one emerald green accent</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -3929,7 +3929,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Hush Fund</t>
+          <t>Burn the Receipts</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>one locked safe forming a protective ring, one emerald green accent</t>
+          <t>one stack of receipts burning inside a protective ring, one emerald green accent</t>
         </is>
       </c>
       <c r="F27" s="4">

--- a/docs/crookedile-card-art-prompts.xlsx
+++ b/docs/crookedile-card-art-prompts.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Art Rules" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Faith Leader" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Celebrity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Nepo Baby" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Art Rules" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faith Leader" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Celebrity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nepo Baby" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Faith Leader'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Celebrity'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Celebrity'!$A$1:$F$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Nepo Baby'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -2279,7 +2279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Rhetoric</t>
+          <t>Pressure</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Rhetoric</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3096,8 +3096,307 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Advance Booking</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E27&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Charm Offensive</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E28&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Disarming Charm</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E29&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Iconic Line</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E30&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Media Training</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E31&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Movie Quote</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Token</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E32&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Never Meet Your Heroes</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E33&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Overpromise</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E34&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Paid-Off Promises</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E35&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Payment Holiday</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E36&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Second Take</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E37&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Signature Catchphrase</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E38&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Victim Narrative</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Rhetoric</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4">
+        <f>Settings!$B$2&amp;" - "&amp;E39&amp;", "&amp;Settings!$B$5&amp;" "&amp;Settings!$B$3&amp;IF(Settings!$B$4&lt;&gt;""," --sref "&amp;Settings!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/docs/crookedile-card-art-prompts.xlsx
+++ b/docs/crookedile-card-art-prompts.xlsx
@@ -4321,7 +4321,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Encore</t>
+          <t>A Second Opinion</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
